--- a/Study2/DataClean_FAVEE_HPP/input_data/dimensions_check_260110.xlsx
+++ b/Study2/DataClean_FAVEE_HPP/input_data/dimensions_check_260110.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SRK\Code\Study2\DataClean_FAVEE_HPP\input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Wanglab\SRK_浣清Haroon【待整理】\github\FAVEE-HPP\Study2\DataClean_FAVEE_HPP\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60743857-6131-4A05-9883-255015003EBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95D7304-DE02-468E-B028-93CB558BC7A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" activeTab="1" xr2:uid="{7515A3A4-785D-467B-9CC5-549D922A846D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{7515A3A4-785D-467B-9CC5-549D922A846D}"/>
   </bookViews>
   <sheets>
     <sheet name="Reversed" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="186">
   <si>
     <t>Valence Evaluation</t>
   </si>
@@ -748,6 +748,10 @@
   </si>
   <si>
     <t>Reverse required: The bipolar of the questionnaire has reversed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intimacy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1529,6 +1533,9 @@
       <c r="D8" t="s">
         <v>91</v>
       </c>
+      <c r="I8" s="18" t="s">
+        <v>185</v>
+      </c>
       <c r="T8" t="s">
         <v>53</v>
       </c>
@@ -2012,6 +2019,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2782,6 +2790,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079757D345F4803458DF839514F8B1E7A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="740138862051a6cbac9fd4e8799d719d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d8c5ae1-d6b2-49fc-a340-c9c2864f432c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aa793588d2a660138d2db8b6d5cf246c" ns2:_="">
     <xsd:import namespace="1d8c5ae1-d6b2-49fc-a340-c9c2864f432c"/>
@@ -2965,15 +2982,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA52D788-9727-417C-9C88-52829AAAB576}">
   <ds:schemaRefs>
@@ -2984,6 +2992,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1FEDEF6-4D29-444B-B0FE-931B6C96AD93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE12F505-0B66-42E6-982A-5A8177C974D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2999,12 +3015,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1FEDEF6-4D29-444B-B0FE-931B6C96AD93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>